--- a/Jiwei/distri_order2/realization3/Cores.xlsx
+++ b/Jiwei/distri_order2/realization3/Cores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,80 +451,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>EM1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>EM2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>EM1</t>
+          <t>X2</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>EM2</t>
+          <t>X3</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>EM3</t>
+          <t>X4</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>X4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>X5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Zeroes</t>
         </is>
